--- a/Paris.xlsx
+++ b/Paris.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={e0cdd91b-276f-4304-90f2-6f65977381fe}</author>
+    <author>tc={07669e3a-aac4-49ca-b06d-a3ab578aedb7}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{e0cdd91b-276f-4304-90f2-6f65977381fe}" ref="E24">
+    <comment authorId="0" xr:uid="{07669e3a-aac4-49ca-b06d-a3ab578aedb7}" ref="E24">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="113">
   <si>
     <t>name</t>
   </si>
@@ -398,6 +398,18 @@
   <si>
     <t>48.877816691549945, 2.33727991474594</t>
   </si>
+  <si>
+    <t>Le Bar à Bulles</t>
+  </si>
+  <si>
+    <t>bar</t>
+  </si>
+  <si>
+    <t>Rooftop bar behind the windmill blades at Moulen Rouge</t>
+  </si>
+  <si>
+    <t>48.88471002715455, 2.332271841758535</t>
+  </si>
 </sst>
 </file>
 
@@ -504,8 +516,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="bill comstock" id="{4ca3f690-ac75-4419-96bc-f5d8b0e183b2}" providerId="google-sheets"/>
-  <x18tc:person displayName="Dev Sherlock" id="{3bcb7a2d-cbef-4162-b916-90c1546f0ef1}" providerId="google-sheets"/>
+  <x18tc:person displayName="bill comstock" id="{8c908f6f-6e4f-455a-9121-8f4567d61e5d}" providerId="google-sheets"/>
+  <x18tc:person displayName="Dev Sherlock" id="{d6c41c52-8068-42d6-9d01-66b2a17dc745}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -705,10 +717,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:15:07.00" personId="{4ca3f690-ac75-4419-96bc-f5d8b0e183b2}" id="{e0cdd91b-276f-4304-90f2-6f65977381fe}" done="1">
+  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:15:07.00" personId="{8c908f6f-6e4f-455a-9121-8f4567d61e5d}" id="{07669e3a-aac4-49ca-b06d-a3ab578aedb7}" done="1">
     <x18tc:text xml:space="preserve">Using Google Maps, right click on a location and the coordinates are displayed. Click on the coordinates and they are copied.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:18:40.00" personId="{3bcb7a2d-cbef-4162-b916-90c1546f0ef1}" id="{fe7ff3e1-93f7-43e9-863f-c55f74e68931}" parentId="{e0cdd91b-276f-4304-90f2-6f65977381fe}">
+  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:18:40.00" personId="{d6c41c52-8068-42d6-9d01-66b2a17dc745}" id="{ba5f9f2e-b36a-4743-9c56-46295b04b6e4}" parentId="{07669e3a-aac4-49ca-b06d-a3ab578aedb7}">
     <x18tc:text xml:space="preserve">Got it thanks!</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -2060,11 +2072,21 @@
       <c r="Y37" s="3"/>
     </row>
     <row r="38">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
+      <c r="A38" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
@@ -28094,8 +28116,9 @@
     <hyperlink r:id="rId6" ref="A35"/>
     <hyperlink r:id="rId7" ref="A36"/>
     <hyperlink r:id="rId8" ref="A37"/>
+    <hyperlink r:id="rId9" ref="A38"/>
   </hyperlinks>
-  <drawing r:id="rId9"/>
-  <legacyDrawing r:id="rId10"/>
+  <drawing r:id="rId10"/>
+  <legacyDrawing r:id="rId11"/>
 </worksheet>
 </file>
--- a/Paris.xlsx
+++ b/Paris.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={e819f632-0617-4659-ad8a-9ecefdbfc37b}</author>
+    <author>tc={39478ca3-3f11-4e07-94d9-17982ca93b2b}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{e819f632-0617-4659-ad8a-9ecefdbfc37b}" ref="E24">
+    <comment authorId="0" xr:uid="{39478ca3-3f11-4e07-94d9-17982ca93b2b}" ref="E24">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="164">
   <si>
     <t>name</t>
   </si>
@@ -255,9 +255,6 @@
   </si>
   <si>
     <t>Le Grand Epicerie de Paris</t>
-  </si>
-  <si>
-    <t>gourmet market</t>
   </si>
   <si>
     <t>Multi-story gourmet food hall and market; lots of food counters to sit and eat, everything from crepes to whelks. We should def plan to get lunch (or dinner) here one day; also great shopping, e.g. food souvenirs (sel de mer, mustard, jams, etc).</t>
@@ -495,9 +492,6 @@
     <t>Puces D'Aligre (flea market)</t>
   </si>
   <si>
-    <t>flea market</t>
-  </si>
-  <si>
     <t>Flea market/vintage (runs on weekdays, most others are weekend-only). Plenty of random art, books, china, maybe a cool ashtray? Plus, lots of good options for lunch afterward in the area. Mostly outdoors, so not for a rainy day.</t>
   </si>
   <si>
@@ -505,9 +499,6 @@
   </si>
   <si>
     <t>Musee du Parfum - Fragonard</t>
-  </si>
-  <si>
-    <t>Museum</t>
   </si>
   <si>
     <t>Small Museum showcasing history of perfumery and olfactory science. Free version or paid tour. Not a must-do but said to be pretty interesting.</t>
@@ -528,7 +519,7 @@
     <t>Armagnac Casterede</t>
   </si>
   <si>
-    <t>Armagnac shop</t>
+    <t>Armagnac</t>
   </si>
   <si>
     <t xml:space="preserve">This one is just for Hambone, if we're in the area. </t>
@@ -538,9 +529,6 @@
   </si>
   <si>
     <t>Maison Ryst-Dupeyron</t>
-  </si>
-  <si>
-    <t>Cognac/Armagnac</t>
   </si>
   <si>
     <t>Possibly a better option (they also bottle their own).</t>
@@ -698,8 +686,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="bill comstock" id="{e9f90229-4b8f-446e-a57c-a96f49fa4923}" providerId="google-sheets"/>
-  <x18tc:person displayName="Dev Sherlock" id="{9cfdfaa7-0dd2-4810-83ad-c9b115aca709}" providerId="google-sheets"/>
+  <x18tc:person displayName="bill comstock" id="{ba129c98-d585-4f5d-9963-152aee599d35}" providerId="google-sheets"/>
+  <x18tc:person displayName="Dev Sherlock" id="{aee0a4e1-05de-42c4-b57d-29a7e5e90404}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -899,10 +887,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:15:07.00" personId="{e9f90229-4b8f-446e-a57c-a96f49fa4923}" id="{e819f632-0617-4659-ad8a-9ecefdbfc37b}" done="1">
+  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:15:07.00" personId="{ba129c98-d585-4f5d-9963-152aee599d35}" id="{39478ca3-3f11-4e07-94d9-17982ca93b2b}" done="1">
     <x18tc:text xml:space="preserve">Using Google Maps, right click on a location and the coordinates are displayed. Click on the coordinates and they are copied.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:18:40.00" personId="{9cfdfaa7-0dd2-4810-83ad-c9b115aca709}" id="{6d6d832c-3170-4a32-aec6-6d6002624b22}" parentId="{e819f632-0617-4659-ad8a-9ecefdbfc37b}">
+  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:18:40.00" personId="{aee0a4e1-05de-42c4-b57d-29a7e5e90404}" id="{4e824f50-ab1b-4782-a8cc-eba95da6bd52}" parentId="{39478ca3-3f11-4e07-94d9-17982ca93b2b}">
     <x18tc:text xml:space="preserve">Got it thanks!</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1757,16 +1745,16 @@
         <v>67</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>69</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F23" s="7" t="b">
         <v>0</v>
@@ -1793,7 +1781,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>42</v>
@@ -1803,7 +1791,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F24" s="7" t="b">
         <v>0</v>
@@ -1830,7 +1818,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>15</v>
@@ -1840,7 +1828,7 @@
         <v>8</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F25" s="7" t="b">
         <v>0</v>
@@ -1867,19 +1855,19 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="C26" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>77</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F26" s="7" t="b">
         <v>0</v>
@@ -1906,7 +1894,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>42</v>
@@ -1916,7 +1904,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F27" s="7" t="b">
         <v>0</v>
@@ -1943,7 +1931,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>42</v>
@@ -1953,7 +1941,7 @@
         <v>8</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F28" s="7" t="b">
         <v>0</v>
@@ -1980,7 +1968,7 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>15</v>
@@ -1990,7 +1978,7 @@
         <v>8</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F29" s="7" t="b">
         <v>0</v>
@@ -2017,19 +2005,19 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="C30" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>87</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F30" s="7" t="b">
         <v>0</v>
@@ -2056,19 +2044,19 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>90</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F31" s="7" t="b">
         <v>0</v>
@@ -2095,19 +2083,19 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F32" s="7" t="b">
         <v>0</v>
@@ -2134,19 +2122,19 @@
     </row>
     <row r="33">
       <c r="A33" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F33" s="7" t="b">
         <v>0</v>
@@ -2173,19 +2161,19 @@
     </row>
     <row r="34">
       <c r="A34" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F34" s="7" t="b">
         <v>0</v>
@@ -2212,19 +2200,19 @@
     </row>
     <row r="35">
       <c r="A35" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F35" s="7" t="b">
         <v>0</v>
@@ -2251,19 +2239,19 @@
     </row>
     <row r="36">
       <c r="A36" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F36" s="7" t="b">
         <v>0</v>
@@ -2290,19 +2278,19 @@
     </row>
     <row r="37">
       <c r="A37" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F37" s="7" t="b">
         <v>0</v>
@@ -2329,19 +2317,19 @@
     </row>
     <row r="38">
       <c r="A38" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="C38" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F38" s="7" t="b">
         <v>0</v>
@@ -2368,19 +2356,19 @@
     </row>
     <row r="39">
       <c r="A39" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F39" s="7" t="b">
         <v>0</v>
@@ -2407,19 +2395,19 @@
     </row>
     <row r="40">
       <c r="A40" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F40" s="7" t="b">
         <v>0</v>
@@ -2446,19 +2434,19 @@
     </row>
     <row r="41">
       <c r="A41" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F41" s="7" t="b">
         <v>0</v>
@@ -2485,19 +2473,19 @@
     </row>
     <row r="42">
       <c r="A42" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F42" s="7" t="b">
         <v>0</v>
@@ -2524,19 +2512,19 @@
     </row>
     <row r="43">
       <c r="A43" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F43" s="7" t="b">
         <v>0</v>
@@ -2563,19 +2551,19 @@
     </row>
     <row r="44">
       <c r="A44" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F44" s="7" t="b">
         <v>0</v>
@@ -2602,19 +2590,19 @@
     </row>
     <row r="45">
       <c r="A45" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F45" s="7" t="b">
         <v>0</v>
@@ -2641,19 +2629,19 @@
     </row>
     <row r="46">
       <c r="A46" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F46" s="7" t="b">
         <v>0</v>
@@ -2680,19 +2668,19 @@
     </row>
     <row r="47">
       <c r="A47" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F47" s="7" t="b">
         <v>0</v>
@@ -2719,19 +2707,19 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>142</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F48" s="7" t="b">
         <v>0</v>
@@ -2758,19 +2746,19 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F49" s="7" t="b">
         <v>0</v>
@@ -2797,19 +2785,19 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F50" s="7" t="b">
         <v>0</v>
@@ -2836,19 +2824,19 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F51" s="7" t="b">
         <v>0</v>
@@ -2875,19 +2863,19 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F52" s="7" t="b">
         <v>0</v>
@@ -2914,19 +2902,19 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F53" s="7" t="b">
         <v>0</v>
@@ -2953,19 +2941,19 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F54" s="7" t="b">
         <v>0</v>
@@ -2992,17 +2980,19 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D55" s="12"/>
+        <v>162</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="E55" s="4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F55" s="7" t="b">
         <v>0</v>

--- a/Paris.xlsx
+++ b/Paris.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={39478ca3-3f11-4e07-94d9-17982ca93b2b}</author>
+    <author>tc={a07a12d1-9018-4a6f-87cf-0762f8d70e96}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{39478ca3-3f11-4e07-94d9-17982ca93b2b}" ref="E24">
+    <comment authorId="0" xr:uid="{a07a12d1-9018-4a6f-87cf-0762f8d70e96}" ref="E24">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="193">
   <si>
     <t>name</t>
   </si>
@@ -338,7 +338,8 @@
       <rPr>
         <sz val="11.0"/>
       </rPr>
-      <t>.)</t>
+      <t>.)
+Dev &amp; Joel visted, May 25, 2026.</t>
     </r>
   </si>
   <si>
@@ -405,7 +406,8 @@
     <t>bar</t>
   </si>
   <si>
-    <t>Rooftop bar behind the windmill blades at Moulen Rouge</t>
+    <t>Rooftop bar behind the windmill blades at Moulen Rouge
+Visted May 25, 2026, sat behind the blades of the windmill. Big fun.</t>
   </si>
   <si>
     <t>48.88471002715455, 2.332271841758535</t>
@@ -563,6 +565,110 @@
   <si>
     <t>48.86462477434395, 2.3620981386226587</t>
   </si>
+  <si>
+    <t>Les Domaines Qui Montent Paris Cardinet</t>
+  </si>
+  <si>
+    <t>Wine store</t>
+  </si>
+  <si>
+    <t>Great selection. Knowledgable helpful staff. Cured meats and cheeses—small but very fine selection. Visited May 18, 2026.</t>
+  </si>
+  <si>
+    <t>48.882116, 2.328847</t>
+  </si>
+  <si>
+    <t>Cafe l'Entracte</t>
+  </si>
+  <si>
+    <t>Bar</t>
+  </si>
+  <si>
+    <t>So small, small selection, neighborhood, great dark hole in the wall. Visited May 18, 2026.</t>
+  </si>
+  <si>
+    <t>48.884068, 2.326317</t>
+  </si>
+  <si>
+    <t>ROOSTER PAR FRÉDÉRIC DUCA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve">After training in prestigious houses (from Passedat to Darroze), Frédéric Duca has set up shop in the more working-class part of the 17th arrondissement. In a former street corner cafe, the Marseille-born chef signs dishes which pay numerous tributes to his Mediterranean and Provençal roots. The lunchtime menu is at delicious eater-friendly prices. More ambitious in the evenings.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">Vistined Thursday, May 21, 2026. </t>
+    </r>
+  </si>
+  <si>
+    <t>48.88687437146972, 2.3131238164807524</t>
+  </si>
+  <si>
+    <t>Le Wagon Bleu</t>
+  </si>
+  <si>
+    <t>Corsican cuisine in a wood-paneled railway carriage which becomes a late-night club on the weekend.
+Great meal with excellent dose of Clementine liquor at meal's end.</t>
+  </si>
+  <si>
+    <t>48.883029954751635, 2.320535551879477</t>
+  </si>
+  <si>
+    <t>La Samaritaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FANCY department store. </t>
+  </si>
+  <si>
+    <t>48.859038971904695, 2.342141408689555</t>
+  </si>
+  <si>
+    <t>Big Love</t>
+  </si>
+  <si>
+    <t>BigLove is a Neapolitan trattoria created by the cheerful Big Mamma team. Through the big glass door on rue Debeylleme, customers are warmly welcomed into an authentic, intimate setting with the feel of a large Italian grocery shop and cosy cafés. BigLove also offers gourmet brunches and traditional Neapolitan dishes, all 100% vegaterian!
+Visted May 19, 2026</t>
+  </si>
+  <si>
+    <t>48.86246746812821, 2.3636752266517496</t>
+  </si>
+  <si>
+    <t>Habib Beirut</t>
+  </si>
+  <si>
+    <t>Lebanese restaurant
+Visited May 17, 2026. Excellent wine, inexpensive, great flavors.</t>
+  </si>
+  <si>
+    <t>48.880146211484224, 2.321841803042917</t>
+  </si>
+  <si>
+    <t>Citypharma</t>
+  </si>
+  <si>
+    <t>Crazy-busy discount drugstore, with floors of toilettries.</t>
+  </si>
+  <si>
+    <t>48.85290456181854, 2.3333528975762388</t>
+  </si>
+  <si>
+    <t>VETRA - Vêtement de travail depuis 1927 - Paris</t>
+  </si>
+  <si>
+    <t>Fancy French "workwear" https://www.vetra.fr/fr/vestes-de-travail-homme/2556-veste-workwear-moleskine-authentique-made-in-france.html</t>
+  </si>
+  <si>
+    <t>48.8616663, 2.3647518</t>
+  </si>
 </sst>
 </file>
 
@@ -630,7 +736,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -668,6 +774,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -686,8 +795,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="bill comstock" id="{ba129c98-d585-4f5d-9963-152aee599d35}" providerId="google-sheets"/>
-  <x18tc:person displayName="Dev Sherlock" id="{aee0a4e1-05de-42c4-b57d-29a7e5e90404}" providerId="google-sheets"/>
+  <x18tc:person displayName="bill comstock" id="{c0958dae-cdf8-4d6a-8a37-447512ed2327}" providerId="google-sheets"/>
+  <x18tc:person displayName="Dev Sherlock" id="{3e126213-f309-41e1-b017-d32923b9c7ca}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -887,10 +996,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:15:07.00" personId="{ba129c98-d585-4f5d-9963-152aee599d35}" id="{39478ca3-3f11-4e07-94d9-17982ca93b2b}" done="1">
+  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:15:07.00" personId="{c0958dae-cdf8-4d6a-8a37-447512ed2327}" id="{a07a12d1-9018-4a6f-87cf-0762f8d70e96}" done="1">
     <x18tc:text xml:space="preserve">Using Google Maps, right click on a location and the coordinates are displayed. Click on the coordinates and they are copied.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:18:40.00" personId="{aee0a4e1-05de-42c4-b57d-29a7e5e90404}" id="{4e824f50-ab1b-4782-a8cc-eba95da6bd52}" parentId="{39478ca3-3f11-4e07-94d9-17982ca93b2b}">
+  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:18:40.00" personId="{3e126213-f309-41e1-b017-d32923b9c7ca}" id="{6e939c0a-c23a-405b-8c12-a3877a6f0735}" parentId="{a07a12d1-9018-4a6f-87cf-0762f8d70e96}">
     <x18tc:text xml:space="preserve">Got it thanks!</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1416,7 +1525,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -1490,7 +1599,7 @@
         <v>45</v>
       </c>
       <c r="F16" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
@@ -1513,7 +1622,7 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1564,7 +1673,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -1757,7 +1866,7 @@
         <v>69</v>
       </c>
       <c r="F23" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -2059,7 +2168,7 @@
         <v>90</v>
       </c>
       <c r="F31" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -2332,7 +2441,7 @@
         <v>112</v>
       </c>
       <c r="F38" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
@@ -2995,7 +3104,7 @@
         <v>163</v>
       </c>
       <c r="F55" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
@@ -3018,12 +3127,24 @@
       <c r="Y55" s="3"/>
     </row>
     <row r="56">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="3"/>
+      <c r="A56" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F56" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -3045,12 +3166,24 @@
       <c r="Y56" s="3"/>
     </row>
     <row r="57">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="3"/>
+      <c r="A57" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F57" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -3072,12 +3205,22 @@
       <c r="Y57" s="3"/>
     </row>
     <row r="58">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="5"/>
+      <c r="A58" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>173</v>
+      </c>
       <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="3"/>
+      <c r="E58" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F58" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -3099,12 +3242,22 @@
       <c r="Y58" s="3"/>
     </row>
     <row r="59">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="5"/>
+      <c r="A59" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>176</v>
+      </c>
       <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="3"/>
+      <c r="E59" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F59" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
@@ -3126,12 +3279,22 @@
       <c r="Y59" s="3"/>
     </row>
     <row r="60">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="5"/>
+      <c r="A60" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>179</v>
+      </c>
       <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="3"/>
+      <c r="E60" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -3153,12 +3316,22 @@
       <c r="Y60" s="3"/>
     </row>
     <row r="61">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="5"/>
+      <c r="A61" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="3"/>
+      <c r="E61" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F61" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -3180,12 +3353,22 @@
       <c r="Y61" s="3"/>
     </row>
     <row r="62">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="5"/>
+      <c r="A62" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>185</v>
+      </c>
       <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="3"/>
+      <c r="E62" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F62" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -3207,12 +3390,22 @@
       <c r="Y62" s="3"/>
     </row>
     <row r="63">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="5"/>
+      <c r="A63" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>188</v>
+      </c>
       <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="3"/>
+      <c r="E63" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F63" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -3234,12 +3427,22 @@
       <c r="Y63" s="3"/>
     </row>
     <row r="64">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="5"/>
+      <c r="A64" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>191</v>
+      </c>
       <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="3"/>
+      <c r="E64" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F64" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -28562,25 +28765,30 @@
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId4" ref="A11"/>
-    <hyperlink r:id="rId5" ref="C20"/>
-    <hyperlink r:id="rId6" ref="C31"/>
-    <hyperlink r:id="rId7" ref="A33"/>
-    <hyperlink r:id="rId8" ref="A34"/>
-    <hyperlink r:id="rId9" ref="A35"/>
-    <hyperlink r:id="rId10" ref="A36"/>
-    <hyperlink r:id="rId11" ref="A37"/>
-    <hyperlink r:id="rId12" ref="A38"/>
-    <hyperlink r:id="rId13" ref="A39"/>
-    <hyperlink r:id="rId14" ref="A40"/>
-    <hyperlink r:id="rId15" ref="A41"/>
-    <hyperlink r:id="rId16" ref="A42"/>
-    <hyperlink r:id="rId17" ref="A43"/>
-    <hyperlink r:id="rId18" ref="A44"/>
-    <hyperlink r:id="rId19" ref="A45"/>
-    <hyperlink r:id="rId20" ref="A46"/>
-    <hyperlink r:id="rId21" ref="A47"/>
+    <hyperlink r:id="rId5" ref="A17"/>
+    <hyperlink r:id="rId6" ref="C20"/>
+    <hyperlink r:id="rId7" ref="C31"/>
+    <hyperlink r:id="rId8" ref="A33"/>
+    <hyperlink r:id="rId9" ref="A34"/>
+    <hyperlink r:id="rId10" ref="A35"/>
+    <hyperlink r:id="rId11" ref="A36"/>
+    <hyperlink r:id="rId12" ref="A37"/>
+    <hyperlink r:id="rId13" ref="A38"/>
+    <hyperlink r:id="rId14" ref="A39"/>
+    <hyperlink r:id="rId15" ref="A40"/>
+    <hyperlink r:id="rId16" ref="A41"/>
+    <hyperlink r:id="rId17" ref="A42"/>
+    <hyperlink r:id="rId18" ref="A43"/>
+    <hyperlink r:id="rId19" ref="A44"/>
+    <hyperlink r:id="rId20" ref="A45"/>
+    <hyperlink r:id="rId21" ref="A46"/>
+    <hyperlink r:id="rId22" ref="A47"/>
+    <hyperlink r:id="rId23" ref="A58"/>
+    <hyperlink r:id="rId24" ref="C58"/>
+    <hyperlink r:id="rId25" ref="C61"/>
+    <hyperlink r:id="rId26" ref="A63"/>
   </hyperlinks>
-  <drawing r:id="rId22"/>
-  <legacyDrawing r:id="rId23"/>
+  <drawing r:id="rId27"/>
+  <legacyDrawing r:id="rId28"/>
 </worksheet>
 </file>
--- a/Paris.xlsx
+++ b/Paris.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={a07a12d1-9018-4a6f-87cf-0762f8d70e96}</author>
+    <author>tc={a566cd20-6bfb-4487-a8b5-cc93b19e0725}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{a07a12d1-9018-4a6f-87cf-0762f8d70e96}" ref="E24">
+    <comment authorId="0" xr:uid="{a566cd20-6bfb-4487-a8b5-cc93b19e0725}" ref="E24">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -795,8 +795,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="bill comstock" id="{c0958dae-cdf8-4d6a-8a37-447512ed2327}" providerId="google-sheets"/>
-  <x18tc:person displayName="Dev Sherlock" id="{3e126213-f309-41e1-b017-d32923b9c7ca}" providerId="google-sheets"/>
+  <x18tc:person displayName="bill comstock" id="{4d7db3e5-4459-46dd-9d4e-578e44a46e9f}" providerId="google-sheets"/>
+  <x18tc:person displayName="Dev Sherlock" id="{1b31b03b-cbad-403a-af47-a1860fc93969}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -996,10 +996,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:15:07.00" personId="{c0958dae-cdf8-4d6a-8a37-447512ed2327}" id="{a07a12d1-9018-4a6f-87cf-0762f8d70e96}" done="1">
+  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:15:07.00" personId="{4d7db3e5-4459-46dd-9d4e-578e44a46e9f}" id="{a566cd20-6bfb-4487-a8b5-cc93b19e0725}" done="1">
     <x18tc:text xml:space="preserve">Using Google Maps, right click on a location and the coordinates are displayed. Click on the coordinates and they are copied.</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:18:40.00" personId="{3e126213-f309-41e1-b017-d32923b9c7ca}" id="{6e939c0a-c23a-405b-8c12-a3877a6f0735}" parentId="{a07a12d1-9018-4a6f-87cf-0762f8d70e96}">
+  <x18tc:threadedComment ref="E24" dT="2026-04-26T15:18:40.00" personId="{1b31b03b-cbad-403a-af47-a1860fc93969}" id="{e9a0f841-9374-4635-822e-2e5b087e0e6d}" parentId="{a566cd20-6bfb-4487-a8b5-cc93b19e0725}">
     <x18tc:text xml:space="preserve">Got it thanks!</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1636,7 +1636,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
